--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40845-2026 artfynd.xlsx
+++ b/artfynd/A 40845-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153211</v>
       </c>
       <c r="B2" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
